--- a/Task1/Оценка_рисков_данных.xlsx
+++ b/Task1/Оценка_рисков_данных.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои_документы\Курсы\Учеба\sprint_7\architecture-propdevelopment\Task1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E637A7FB-D485-472A-94C3-632CBB009E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="22995" windowHeight="10815"/>
+    <workbookView xWindow="1200" yWindow="2655" windowWidth="18000" windowHeight="9480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="24">
   <si>
     <t>Данные</t>
   </si>
@@ -82,12 +88,18 @@
   </si>
   <si>
     <t>Незначительный</t>
+  </si>
+  <si>
+    <t>Данные содержащие коммерческую тайну и финансовые отчеты компании</t>
+  </si>
+  <si>
+    <t>Данные хранилища содержащего системные секреты, пароли, ключи сертификатов</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -174,6 +186,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -221,7 +236,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -254,9 +269,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -289,6 +321,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -464,8 +513,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" style="4" customWidth="1"/>
@@ -688,7 +737,7 @@
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>11</v>
       </c>
@@ -722,7 +771,7 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>12</v>
       </c>
@@ -765,7 +814,7 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" ht="36.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>13</v>
       </c>
@@ -886,6 +935,82 @@
         <v>5</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -896,7 +1021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -905,7 +1030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
